--- a/NECP Scenario/Results/Regional Results/SAMOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/SAMOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.434376155887663E-08</v>
+        <v>5.06820317178718E-08</v>
       </c>
       <c r="C3">
-        <v>2.029611706190806E-08</v>
+        <v>2.994971112861222E-08</v>
       </c>
       <c r="D3">
-        <v>0.05812508457842622</v>
+        <v>0.0611747241882893</v>
       </c>
       <c r="E3">
-        <v>0.0497953369030564</v>
+        <v>0.05191692511330053</v>
       </c>
       <c r="F3">
-        <v>0.05158827535656905</v>
+        <v>0.05691752346018365</v>
       </c>
       <c r="G3">
-        <v>0.1335571353288528</v>
+        <v>0.1251942215860224</v>
       </c>
       <c r="H3">
-        <v>0.1392124360954331</v>
+        <v>0.1349722222138927</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.919219732726698E-08</v>
+        <v>4.307972696199111E-08</v>
       </c>
       <c r="C4">
-        <v>1.725169950484369E-08</v>
+        <v>2.545725446112044E-08</v>
       </c>
       <c r="D4">
-        <v>0.04940632189170156</v>
+        <v>0.05199851556004358</v>
       </c>
       <c r="E4">
-        <v>0.04232603636761252</v>
+        <v>0.0441293863463072</v>
       </c>
       <c r="F4">
-        <v>0.04385003405307158</v>
+        <v>0.04837989494115472</v>
       </c>
       <c r="G4">
-        <v>0.1135235650295717</v>
+        <v>0.1064150883481187</v>
       </c>
       <c r="H4">
-        <v>0.1183305706811364</v>
+        <v>0.1147263888818101</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.1159803970184818</v>
+        <v>0.1159803989639527</v>
       </c>
       <c r="C14">
-        <v>0.1319652649279638</v>
+        <v>0.1319652657854835</v>
       </c>
       <c r="D14">
-        <v>0.1456354379689024</v>
+        <v>0.1456354279608691</v>
       </c>
       <c r="E14">
-        <v>0.1749638285387667</v>
+        <v>0.146059342950142</v>
       </c>
       <c r="F14">
-        <v>0.1731531549816946</v>
+        <v>0.1684517191982701</v>
       </c>
       <c r="G14">
-        <v>0.2056058987560844</v>
+        <v>0.2056059381127493</v>
       </c>
       <c r="H14">
-        <v>0.2704718327399354</v>
+        <v>0.2704720586363105</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.316355113209441</v>
+        <v>0.3163551370041707</v>
       </c>
       <c r="C28">
-        <v>0.3737548442562006</v>
+        <v>0.3737548555285045</v>
       </c>
       <c r="D28">
-        <v>0.08674759977022196</v>
+        <v>0.08449975652517641</v>
       </c>
       <c r="E28">
-        <v>4.054944910062275E-08</v>
+        <v>6.001753950520144E-08</v>
       </c>
       <c r="F28">
-        <v>4.137647111034721E-08</v>
+        <v>6.084980847774598E-08</v>
       </c>
       <c r="G28">
-        <v>4.701409631963189E-08</v>
+        <v>6.937194314281083E-08</v>
       </c>
       <c r="H28">
-        <v>6.50654191398301E-05</v>
+        <v>3.847829524573313E-07</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.08987361169735658</v>
+        <v>0.08987361845253425</v>
       </c>
       <c r="C29">
-        <v>0.1061803534767163</v>
+        <v>0.1061803566766208</v>
       </c>
       <c r="D29">
-        <v>0.02464420447258641</v>
+        <v>0.02400561263799429</v>
       </c>
       <c r="E29">
-        <v>1.150857683576884E-08</v>
+        <v>1.703396750595466E-08</v>
       </c>
       <c r="F29">
-        <v>1.173828108617286E-08</v>
+        <v>1.726266406274053E-08</v>
       </c>
       <c r="G29">
-        <v>1.333216844571693E-08</v>
+        <v>1.96723425417309E-08</v>
       </c>
       <c r="H29">
-        <v>1.848434784838351E-05</v>
+        <v>1.090974874177607E-07</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.08030404679038147</v>
+        <v>0.08239864966908649</v>
       </c>
       <c r="E30">
-        <v>0.08806850123465969</v>
+        <v>0.09010563728339231</v>
       </c>
       <c r="F30">
-        <v>0.1058157421542779</v>
+        <v>0.1079514585973224</v>
       </c>
       <c r="G30">
-        <v>0.1804697379023247</v>
+        <v>0.1583182599171694</v>
       </c>
       <c r="H30">
-        <v>0.1942241060382786</v>
+        <v>0.1884601507998265</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.006461362699760451</v>
+        <v>0.006461358754027642</v>
       </c>
       <c r="C31">
-        <v>0.00646570773844526</v>
+        <v>0.006465704684380231</v>
       </c>
       <c r="D31">
-        <v>0.005353793382552062</v>
+        <v>0.005365605021624067</v>
       </c>
       <c r="E31">
-        <v>0.006648812083027271</v>
+        <v>0.006648293398109467</v>
       </c>
       <c r="F31">
-        <v>0.006648270532114283</v>
+        <v>0.006647260147840419</v>
       </c>
       <c r="G31">
-        <v>0.006647226958683115</v>
+        <v>0.00664586107011591</v>
       </c>
       <c r="H31">
-        <v>0.006635386120609086</v>
+        <v>0.006627633514826051</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4.771433571256001E-08</v>
+        <v>7.154088328086417E-08</v>
       </c>
       <c r="E32">
-        <v>1.20406676343776E-06</v>
+        <v>0.02903549738489125</v>
       </c>
       <c r="F32">
-        <v>0.04005820280059009</v>
+        <v>0.04492029411440698</v>
       </c>
       <c r="G32">
-        <v>0.0481426427192226</v>
+        <v>0.04814261521156837</v>
       </c>
       <c r="H32">
-        <v>0.04835638463801138</v>
+        <v>0.04835621271451766</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.006819743458289211</v>
+        <v>0.006819741529220488</v>
       </c>
       <c r="C33">
-        <v>0.006833167765463422</v>
+        <v>0.006833166916511755</v>
       </c>
       <c r="D33">
-        <v>0.006843796177829925</v>
+        <v>0.006843782371985858</v>
       </c>
       <c r="E33">
-        <v>0.006865889226497322</v>
+        <v>0.006736081515652865</v>
       </c>
       <c r="F33">
-        <v>0.006677198668173841</v>
+        <v>0.006516543165194012</v>
       </c>
       <c r="G33">
-        <v>0.006685076999811061</v>
+        <v>0.006685065191081329</v>
       </c>
       <c r="H33">
-        <v>0.006775991842197682</v>
+        <v>0.006775938113382417</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.03279186411981785</v>
+        <v>0.0317385565811807</v>
       </c>
       <c r="E36">
-        <v>0.2833032757002046</v>
+        <v>0.2603958449538185</v>
       </c>
       <c r="F36">
-        <v>0.3104472895224646</v>
+        <v>0.2883832353925749</v>
       </c>
       <c r="G36">
-        <v>0.3083063196238147</v>
+        <v>0.2874578180924712</v>
       </c>
       <c r="H36">
-        <v>0.3064579243767147</v>
+        <v>0.2842953427167489</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.02201237468530401</v>
+        <v>0.02201237632827693</v>
       </c>
       <c r="C37">
-        <v>0.02201237544719937</v>
+        <v>0.02201237763307501</v>
       </c>
       <c r="D37">
-        <v>0.01423244371214465</v>
+        <v>0.01427536430959526</v>
       </c>
       <c r="E37">
-        <v>0.01912901636439502</v>
+        <v>0.01899654762062104</v>
       </c>
       <c r="F37">
-        <v>0.01913438649168637</v>
+        <v>0.01867184642651659</v>
       </c>
       <c r="G37">
-        <v>0.01895335797740299</v>
+        <v>0.01866829595784658</v>
       </c>
       <c r="H37">
-        <v>0.01908240480998145</v>
+        <v>0.01850992687009986</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.0002678835583711533</v>
+        <v>0.000267887790199785</v>
       </c>
       <c r="C38">
-        <v>0.0002501134506168047</v>
+        <v>0.0002501151677578738</v>
       </c>
       <c r="D38">
-        <v>0.03319630460376097</v>
+        <v>0.03245731770381324</v>
       </c>
       <c r="E38">
-        <v>0.03207752164231019</v>
+        <v>0.03220531920021561</v>
       </c>
       <c r="F38">
-        <v>0.03137586915300015</v>
+        <v>0.03906935040851665</v>
       </c>
       <c r="G38">
-        <v>0.03898780446376668</v>
+        <v>0.03949976669172686</v>
       </c>
       <c r="H38">
-        <v>0.04042778072665035</v>
+        <v>0.04874785686664316</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.434376155887663E-08</v>
+        <v>5.06820317178718E-08</v>
       </c>
       <c r="C40">
-        <v>2.029611706190806E-08</v>
+        <v>2.994971112861222E-08</v>
       </c>
       <c r="D40">
-        <v>0.05812508457842622</v>
+        <v>0.0611747241882893</v>
       </c>
       <c r="E40">
-        <v>0.0497953369030564</v>
+        <v>0.05191692511330053</v>
       </c>
       <c r="F40">
-        <v>0.05158827535656905</v>
+        <v>0.05691752346018365</v>
       </c>
       <c r="G40">
-        <v>0.1335571353288528</v>
+        <v>0.1251942215860224</v>
       </c>
       <c r="H40">
-        <v>0.1392124360954331</v>
+        <v>0.1349722222138927</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2.919219732726698E-08</v>
+        <v>4.307972696199111E-08</v>
       </c>
       <c r="C41">
-        <v>1.725169950484369E-08</v>
+        <v>2.545725446112044E-08</v>
       </c>
       <c r="D41">
-        <v>0.04940632189170156</v>
+        <v>0.05199851556004358</v>
       </c>
       <c r="E41">
-        <v>0.04232603636761252</v>
+        <v>0.0441293863463072</v>
       </c>
       <c r="F41">
-        <v>0.04385003405307158</v>
+        <v>0.04837989494115472</v>
       </c>
       <c r="G41">
-        <v>0.1135235650295717</v>
+        <v>0.1064150883481187</v>
       </c>
       <c r="H41">
-        <v>0.1183305706811364</v>
+        <v>0.1147263888818101</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.151564231609654E-09</v>
+        <v>-7.602304755880696E-09</v>
       </c>
       <c r="C42">
-        <v>-3.044417557064368E-09</v>
+        <v>-4.492456667491785E-09</v>
       </c>
       <c r="D42">
-        <v>-0.008718762686724668</v>
+        <v>-0.009176208628245718</v>
       </c>
       <c r="E42">
-        <v>-0.007469300535443882</v>
+        <v>-0.007787538766993334</v>
       </c>
       <c r="F42">
-        <v>-0.007738241303497477</v>
+        <v>-0.008537628519028936</v>
       </c>
       <c r="G42">
-        <v>-0.02003357029928103</v>
+        <v>-0.01877913323790373</v>
       </c>
       <c r="H42">
-        <v>-0.02088186541429669</v>
+        <v>-0.02024583333208256</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-0.211145797398939</v>
+        <v>-0.2193186555976786</v>
       </c>
       <c r="F43">
-        <v>-0.2576205662391078</v>
+        <v>-0.2412266798369591</v>
       </c>
       <c r="G43">
-        <v>-0.2845411479042277</v>
+        <v>-0.242509143681133</v>
       </c>
       <c r="H43">
-        <v>-0.2295447737054401</v>
+        <v>-0.2016554323423532</v>
       </c>
     </row>
     <row r="44" spans="1:8">
